--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FEDDF1-1C66-4FAF-9094-A5D2E5CC28F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE72CE29-658C-474D-B075-0BA82D07DA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12510" yWindow="1440" windowWidth="14385" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6375" yWindow="1050" windowWidth="15465" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -46,19 +46,21 @@
     <t>고유 ID</t>
   </si>
   <si>
-    <t>(name)</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
     <t>4월 6일 월요일 오전 2시 36분</t>
   </si>
   <si>
-    <t>dateDialogue_Opening_1_1_100</t>
+    <t>Description</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Description</t>
+    <t>dateDialogue_Opening_1_1_100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(name)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -366,7 +368,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -375,7 +377,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -618,10 +620,10 @@
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -630,13 +632,13 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1">
@@ -644,7 +646,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>0</v>
@@ -667,7 +669,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE72CE29-658C-474D-B075-0BA82D07DA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9B784B-C56E-4071-9AF5-9D561D77922E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6375" yWindow="1050" windowWidth="15465" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="1740" windowWidth="23505" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
-  <si>
-    <t>SelectionNameList</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>CharacterDataId</t>
   </si>
@@ -63,12 +60,24 @@
     <t>(name)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NextDialogueId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_99</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -93,6 +102,12 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -162,7 +177,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -185,6 +200,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -602,7 +618,7 @@
   <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="77.140625" customWidth="1"/>
     <col min="5" max="6" width="50.7109375" customWidth="1"/>
@@ -610,7 +626,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -620,56 +636,59 @@
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
+      <c r="C4" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9B784B-C56E-4071-9AF5-9D561D77922E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8FBF10-1048-4B91-AB35-D4CDE597CE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1740" windowWidth="23505" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2235" yWindow="1650" windowWidth="23505" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8FBF10-1048-4B91-AB35-D4CDE597CE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A72818-2643-4FA3-9640-CD1C3D06393B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2235" yWindow="1650" windowWidth="23505" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="990" yWindow="1380" windowWidth="27255" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -20,24 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>CharacterDataId</t>
   </si>
   <si>
     <t>Id</t>
-  </si>
-  <si>
-    <t>SelectionDialogueIdList</t>
-  </si>
-  <si>
-    <t>string[]</t>
-  </si>
-  <si>
-    <t>VoicePath</t>
-  </si>
-  <si>
-    <t>TexturePath</t>
   </si>
   <si>
     <t>고유 ID</t>
@@ -69,7 +57,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>mindDialogue_Opening_1_1_99</t>
+    <t>mindDialogue_Opening_1_1_101</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -615,377 +603,261 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="35.85546875" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="77.140625" customWidth="1"/>
-    <col min="5" max="6" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="77.140625" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
+      <c r="D3" s="2" t="s">
+        <v>0</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="C4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1">
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1">
+    </row>
+    <row r="35" spans="1:4" ht="15.75" customHeight="1">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1"/>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A72818-2643-4FA3-9640-CD1C3D06393B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F201D7-94AE-4B24-AEE3-92B9D1603C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="990" yWindow="1380" windowWidth="27255" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="2250" windowWidth="28185" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>CharacterDataId</t>
   </si>
@@ -58,6 +58,18 @@
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dateDialogue_Opening_1_1_175</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월 6일 월요일 오전 9시 30분</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_176</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -607,7 +619,7 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="35.85546875" customWidth="1"/>
-    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="77.140625" customWidth="1"/>
     <col min="4" max="4" width="23.5703125" customWidth="1"/>
   </cols>
@@ -660,9 +672,15 @@
       <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A72818-2643-4FA3-9640-CD1C3D06393B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C7BA69-859F-4B52-996C-7341F34AD853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="990" yWindow="1380" windowWidth="27255" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
-  <si>
-    <t>CharacterDataId</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -58,6 +55,26 @@
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dateDialogue_Opening_1_1_175</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월 6일 월요일 오전 9시 30분</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_176</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGImagePath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Dark empty Room</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -607,63 +624,73 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="35.85546875" customWidth="1"/>
-    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="77.140625" customWidth="1"/>
     <col min="4" max="4" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>0</v>
+      <c r="D4" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="10" t="s">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="3"/>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C7BA69-859F-4B52-996C-7341F34AD853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D144C2-E779-498B-AA1C-B35B30794C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>Id</t>
   </si>
@@ -75,6 +75,14 @@
   </si>
   <si>
     <t>Sprite/Dark empty Room</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dateDialogue_Opening_1_1_286</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월 7일 화요일 오전 7시 30분</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -693,8 +701,12 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+      <c r="A6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="4"/>
     </row>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D144C2-E779-498B-AA1C-B35B30794C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3887E7BC-BA98-4A6F-BAA1-1F86531CDC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1710" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1170" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
+    <sheet name="Table_DateDialogue" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>Id</t>
   </si>
@@ -83,6 +83,10 @@
   </si>
   <si>
     <t>4월 7일 화요일 오전 7시 30분</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mindDialogue_Opening_1_1_287</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -707,8 +711,12 @@
       <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="3"/>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3887E7BC-BA98-4A6F-BAA1-1F86531CDC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1170" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1560" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_DateDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3887E7BC-BA98-4A6F-BAA1-1F86531CDC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1560" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="780" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_DateDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3887E7BC-BA98-4A6F-BAA1-1F86531CDC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="780" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_DateDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3887E7BC-BA98-4A6F-BAA1-1F86531CDC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02250816-8E18-4DDB-8A58-14E14A0602E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>Id</t>
   </si>
@@ -87,6 +87,50 @@
   </si>
   <si>
     <t>mindDialogue_Opening_1_1_287</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dateDialogue_Ending_1_1_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월 9일 화요일 오전 8시 00분</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dateDialogue_Ending_1_1_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 용기를 내어 변화된 내 모습으로 그녀를 다시 찾아갔다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dateDialogue_Ending_1_1_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그녀에게 변화된 내가 좋게 보여지길 바란다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_1_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dateDialogue_Ending_1_2_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dateDialogue_Ending_1_2_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dateDialogue_Ending_1_2_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDialogue_Ending_1_2_4</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -719,40 +763,88 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A8" s="3"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="A8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A9" s="3"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="3"/>
+      <c r="A9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A10" s="3"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
+      <c r="A10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
+      <c r="A11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="A12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02250816-8E18-4DDB-8A58-14E14A0602E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05929C1-B74B-4EFF-BD6D-569B06EE49B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,10 +94,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>4월 9일 화요일 오전 8시 00분</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>dateDialogue_Ending_1_1_2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -131,6 +127,10 @@
   </si>
   <si>
     <t>normalDialogue_Ending_1_2_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4월 10일 수요일 오전 8시 00분</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -767,10 +767,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>14</v>
@@ -778,13 +778,13 @@
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>14</v>
@@ -792,13 +792,13 @@
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>14</v>
@@ -806,13 +806,13 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>14</v>
@@ -820,13 +820,13 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>14</v>
@@ -834,13 +834,13 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>14</v>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05929C1-B74B-4EFF-BD6D-569B06EE49B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="870" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_DateDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05929C1-B74B-4EFF-BD6D-569B06EE49B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1ABBB7-AE16-4FDC-89CF-33E9BF9E667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="870" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="435" yWindow="1080" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_DateDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1ABBB7-AE16-4FDC-89CF-33E9BF9E667E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C38D1A-AD0B-4D96-99EB-9C0E694CD720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="435" yWindow="1080" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_DateDialogue" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/0_DateDialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C38D1A-AD0B-4D96-99EB-9C0E694CD720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729850DB-00D3-45BF-A72D-57551B71CF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -130,7 +130,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>4월 10일 수요일 오전 8시 00분</t>
+    <t>4월 10일 수요일 결전의 날</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
